--- a/HCVData/subtyping-comparison-all-ras/11-report-subtype-agreement/NS5A_CometFullSeqSubtype_4R_Subtyping_Distances.xlsx
+++ b/HCVData/subtyping-comparison-all-ras/11-report-subtype-agreement/NS5A_CometFullSeqSubtype_4R_Subtyping_Distances.xlsx
@@ -431,65 +431,70 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Genotype1Distance</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Genotype2Distance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Genotype3Distance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Genotype4Distance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Genotype5Distance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Genotype6Distance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Genotype7Distance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Genotype8Distance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FirstChoiceGenotype</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>SecondChoiceGenotype</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -503,55 +508,60 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>24.242</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>32.628</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>25.378</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>29.167</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>30.909</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>30.605</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>24.242</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>25.378</t>
         </is>
@@ -565,55 +575,60 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>23.030</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>30.565</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>23.867</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>28.571</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>30.000</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>30.887</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>23.030</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>23.867</t>
         </is>
@@ -627,55 +642,60 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>23.939</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>32.482</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>23.867</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>29.483</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>30.000</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>32.110</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>23.939</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>23.867</t>
         </is>
@@ -689,55 +709,60 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>24.242</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>32.482</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>24.773</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>29.483</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>30.303</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>32.416</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>24.242</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>24.773</t>
         </is>
@@ -751,55 +776,60 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>24.012</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>32.482</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>23.750</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>30.488</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>30.357</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>31.387</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>24.012</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>23.750</t>
         </is>
@@ -813,55 +843,60 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>23.636</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>31.522</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>23.565</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>28.746</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>31.515</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>30.606</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>23.636</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>23.565</t>
         </is>
@@ -875,60 +910,65 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>22.424</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>32.831</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>31.159</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>22.741</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>29.664</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>30.909</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>29.808</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>22.424</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>22.741</t>
         </is>
@@ -942,60 +982,65 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>24.924</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>34.545</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>31.481</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>23.676</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>28.659</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>30.631</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>30.068</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>24.924</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>23.676</t>
         </is>
@@ -1009,60 +1054,65 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>23.750</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>32.937</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>30.435</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>24.901</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>28.340</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>29.268</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>33.333</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>23.750</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>24.901</t>
         </is>
@@ -1089,150 +1139,155 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype1aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype1aDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype1bDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype1bDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype1cDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype1cDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype1dDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype1eDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype1eDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype1gDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype1gDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype1hDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype1hDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype1iDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype1jDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype1kDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype1lDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype1lDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype1mDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype1mDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype1nDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype1nDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype1oDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Subtype1oDistance</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -1246,150 +1301,155 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>25.152</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>25.152</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>24.096</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>24.096</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>25.994</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>24.126</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>24.126</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>23.158</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>23.158</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>26.970</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>24.561</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>24.620</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>24.096</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>1k</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>24.620</t>
         </is>
@@ -1403,150 +1463,155 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>23.939</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>23.939</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>25.301</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>25.301</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>26.911</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>24.211</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>24.211</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>26.761</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>26.761</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>26.970</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>24.316</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>29.697</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>29.697</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>23.939</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>1k</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>24.316</t>
         </is>
@@ -1560,150 +1625,155 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>25.688</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>24.211</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>24.211</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>28.614</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>28.614</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>29.091</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>25.228</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>25.879</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>25.879</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>27.044</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>27.044</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>29.518</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>29.518</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
@@ -1717,150 +1787,155 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>25.152</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>25.152</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>25.602</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>25.602</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>25.688</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>24.561</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>24.561</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>26.364</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>26.364</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>28.313</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>28.313</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>29.091</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>26.140</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>25.879</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>25.879</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>29.819</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>29.819</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>25.152</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>25.602</t>
         </is>
@@ -1874,150 +1949,155 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>25.228</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>25.228</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>25.982</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>25.982</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>28.115</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>28.115</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>26.415</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>24.390</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>24.390</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>26.606</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>26.606</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>26.056</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>26.056</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>29.179</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>27.964</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>24.699</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>25.559</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>25.559</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>27.052</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>27.052</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>28.875</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>28.875</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>27.660</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>27.660</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1k</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>24.699</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>25.228</t>
         </is>
@@ -2031,150 +2111,155 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>25.301</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>25.301</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>26.300</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>24.825</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>24.825</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>25.758</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>25.758</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>27.410</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>27.410</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>27.879</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>27.879</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>26.140</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>26.518</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>26.518</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>27.879</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>27.879</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>28.873</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>28.873</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>26.667</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>26.667</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>25.301</t>
         </is>
@@ -2188,150 +2273,155 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>23.636</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>23.636</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>24.699</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>24.699</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>27.389</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>27.389</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>25.714</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>23.509</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>23.509</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>25.455</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>25.455</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>27.108</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>27.108</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>26.970</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>24.316</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>25.240</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>25.240</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>26.364</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>26.364</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>29.091</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>29.091</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>25.758</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>25.758</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>23.636</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>1k</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>24.316</t>
         </is>
@@ -2345,150 +2435,155 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>25.532</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>25.532</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>24.296</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>24.296</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>27.476</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>27.476</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>26.250</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>24.561</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>24.561</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>25.994</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>25.994</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>27.795</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>27.795</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>27.829</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>28.875</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>25.455</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>26.837</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>26.837</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>27.356</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>27.356</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>28.313</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>28.313</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>26.748</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>26.748</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1k</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>25.455</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>25.532</t>
         </is>
@@ -2502,150 +2597,155 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>22.944</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>22.944</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>22.619</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>22.619</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>25.523</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>25.523</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>24.603</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>25.794</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>25.794</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>25.847</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>25.847</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>23.750</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>26.407</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>25.108</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>25.896</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>25.896</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>26.339</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>26.339</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>29.167</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>29.167</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>26.190</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>26.190</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>22.619</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>24.603</t>
         </is>
@@ -2672,145 +2772,150 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype2aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype2aDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype2bDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype2bDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype2cDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype2dDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype2eDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype2fDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype2fDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype2iDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype2jDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype2jDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype2kDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype2lDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype2lDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype2mDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype2mDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype2qDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype2qDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype2rDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype2tDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype2uDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype2vDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -2837,85 +2942,90 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype3aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype3bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype3dDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype3eDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype3gDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype3gDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype3hDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype3iDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype3iDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype3kDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype3kDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -2942,145 +3052,150 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype4aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype4bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype4cDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype4dDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype4dDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype4fDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype4fDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype4gDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype4kDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype4kDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype4lDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype4mDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype4nDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype4oDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype4pDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype4qDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype4rDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype4sDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype4tDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype4vDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype4vDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype4wDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype4wDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -3107,40 +3222,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype5aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype5bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -3167,255 +3287,260 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype6aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype6aDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype6bDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype6cDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype6dDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype6eDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype6fDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype6gDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype6hDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype6iDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype6jDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype6kDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype6lDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype6mDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype6nDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype6nDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype6oDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype6pDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype6qDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype6rDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype6sDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype6tDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype6tDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Subtype6uDistance</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Subtype6vDistance</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Subtype6vDistance</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Subtype6wDistance</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Subtype6wDistance</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Subtype6xaDistance</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Subtype6xaDistance</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Subtype6xbDistance</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Subtype6xbDistance</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Subtype6xcDistance</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Subtype6xdDistance</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Subtype6xdDistance</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Subtype6xeDistance</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Subtype6xeDistance</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Subtype6xfDistance</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Subtype6xfDistance</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Subtype6xgDistance</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Subtype6xgDistance</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Subtype6xhDistance</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Subtype6xiDistance</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Subtype6xiDistance</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Subtype6xjDistance</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -3442,40 +3567,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype7aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype7bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -3502,35 +3632,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype8aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>

--- a/HCVData/subtyping-comparison-all-ras/11-report-subtype-agreement/NS5A_CometFullSeqSubtype_4R_Subtyping_Distances.xlsx
+++ b/HCVData/subtyping-comparison-all-ras/11-report-subtype-agreement/NS5A_CometFullSeqSubtype_4R_Subtyping_Distances.xlsx
@@ -9,13 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genotype" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_7" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_8" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2754,924 +2747,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype2aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype2aDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype2bDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype2bDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype2cDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype2dDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype2eDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype2fDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype2fDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype2iDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype2jDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Subtype2jDistance</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Subtype2kDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Subtype2lDistance</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Subtype2lDistance</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Subtype2mDistance</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Subtype2mDistance</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Subtype2qDistance</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Subtype2qDistance</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Subtype2rDistance</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Subtype2tDistance</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Subtype2uDistance</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Subtype2vDistance</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype3aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype3bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype3dDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype3eDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype3gDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype3gDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype3hDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype3iDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype3iDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype3kDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype3kDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype4aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype4bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype4cDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype4dDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype4dDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype4fDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype4fDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype4gDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype4kDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype4kDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype4lDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Subtype4mDistance</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Subtype4nDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Subtype4oDistance</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Subtype4pDistance</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Subtype4qDistance</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Subtype4rDistance</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Subtype4sDistance</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Subtype4tDistance</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Subtype4vDistance</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Subtype4vDistance</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Subtype4wDistance</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Subtype4wDistance</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype5aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype5bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype6aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype6aDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype6bDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype6cDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype6dDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype6eDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype6fDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype6gDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype6hDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype6iDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype6jDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Subtype6kDistance</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Subtype6lDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Subtype6mDistance</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Subtype6nDistance</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Subtype6nDistance</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Subtype6oDistance</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Subtype6pDistance</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Subtype6qDistance</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Subtype6rDistance</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Subtype6sDistance</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Subtype6tDistance</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Subtype6tDistance</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Subtype6uDistance</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Subtype6vDistance</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Subtype6vDistance</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Subtype6wDistance</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Subtype6wDistance</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Subtype6xaDistance</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Subtype6xaDistance</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Subtype6xbDistance</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Subtype6xbDistance</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Subtype6xcDistance</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>Subtype6xdDistance</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Subtype6xdDistance</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Subtype6xeDistance</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>Subtype6xeDistance</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>Subtype6xfDistance</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Subtype6xfDistance</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Subtype6xgDistance</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Subtype6xgDistance</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Subtype6xhDistance</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Subtype6xiDistance</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>Subtype6xiDistance</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>Subtype6xjDistance</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype7aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype7bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype8aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>